--- a/backend/data/financials_by_company/1AG1.MI.xlsx
+++ b/backend/data/financials_by_company/1AG1.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,582 +662,638 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-438905.61</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.16797</v>
-      </c>
-      <c r="D2" t="n">
-        <v>97150000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2613000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2613000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44925000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5547187000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>94537000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>49612000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-15873000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8984000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>23068094.39</v>
-      </c>
-      <c r="P2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6228313000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>216190000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>216190000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>20894000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4218000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>25112000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1548000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1548000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>-15873000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>357000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>8984000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>43598000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>681126000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>160924000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>44925000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>44925000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>151374000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>140981000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10393000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>724724000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5547187000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6271911000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6271911000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>1355000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-60892.65</v>
+        <v>-317856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01365</v>
+        <v>0.0308</v>
       </c>
       <c r="D3" t="n">
-        <v>-52054000</v>
+        <v>-178620000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4461000</v>
+        <v>-10320000</v>
       </c>
       <c r="F3" t="n">
-        <v>-4461000</v>
+        <v>-10320000</v>
       </c>
       <c r="G3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="H3" t="n">
-        <v>42929000</v>
+        <v>36748000</v>
       </c>
       <c r="I3" t="n">
-        <v>4934947000</v>
+        <v>6045907000</v>
       </c>
       <c r="J3" t="n">
-        <v>-56515000</v>
+        <v>-188940000</v>
       </c>
       <c r="K3" t="n">
-        <v>-99444000</v>
+        <v>-225688000</v>
       </c>
       <c r="L3" t="n">
-        <v>-11291000</v>
+        <v>-19277000</v>
       </c>
       <c r="M3" t="n">
-        <v>18634000</v>
+        <v>13322000</v>
       </c>
       <c r="N3" t="n">
-        <v>8160000</v>
+        <v>1005000</v>
       </c>
       <c r="O3" t="n">
-        <v>-112065892.65</v>
+        <v>-236369856</v>
       </c>
       <c r="P3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5565161000</v>
+        <v>6743531000</v>
       </c>
       <c r="R3" t="n">
-        <v>214906000</v>
+        <v>213828000</v>
       </c>
       <c r="S3" t="n">
-        <v>214906000</v>
+        <v>213828000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.54</v>
+        <v>-1.15</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.54</v>
+        <v>-1.15</v>
       </c>
       <c r="V3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="W3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-116466000</v>
+        <v>-246372000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1612000</v>
+        <v>7362000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-118078000</v>
+        <v>-239010000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3790000</v>
+        <v>-10320000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3790000</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>10320000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3450000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>-11291000</v>
+        <v>-19277000</v>
       </c>
       <c r="AH3" t="n">
-        <v>817000</v>
+        <v>6960000</v>
       </c>
       <c r="AI3" t="n">
-        <v>18634000</v>
+        <v>13322000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8160000</v>
+        <v>1005000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-102326000</v>
+        <v>-209412000</v>
       </c>
       <c r="AL3" t="n">
-        <v>630214000</v>
+        <v>697624000</v>
       </c>
       <c r="AM3" t="n">
-        <v>146902000</v>
+        <v>168493000</v>
       </c>
       <c r="AN3" t="n">
-        <v>42929000</v>
+        <v>36748000</v>
       </c>
       <c r="AO3" t="n">
-        <v>42929000</v>
+        <v>36748000</v>
       </c>
       <c r="AP3" t="n">
-        <v>147593000</v>
+        <v>205084000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>137067000</v>
+        <v>193156000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10526000</v>
+        <v>11928000</v>
       </c>
       <c r="AS3" t="n">
-        <v>527888000</v>
+        <v>488212000</v>
       </c>
       <c r="AT3" t="n">
-        <v>4934947000</v>
+        <v>6045907000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5462835000</v>
+        <v>6534119000</v>
       </c>
       <c r="AV3" t="n">
-        <v>5462835000</v>
+        <v>6534119000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-317856</v>
+        <v>-60892.65</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0308</v>
+        <v>0.01365</v>
       </c>
       <c r="D4" t="n">
-        <v>-178620000</v>
+        <v>-52054000</v>
       </c>
       <c r="E4" t="n">
-        <v>-10320000</v>
+        <v>-4461000</v>
       </c>
       <c r="F4" t="n">
-        <v>-10320000</v>
+        <v>-4461000</v>
       </c>
       <c r="G4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="H4" t="n">
-        <v>36748000</v>
+        <v>42929000</v>
       </c>
       <c r="I4" t="n">
-        <v>6045907000</v>
+        <v>4934947000</v>
       </c>
       <c r="J4" t="n">
-        <v>-188940000</v>
+        <v>-56515000</v>
       </c>
       <c r="K4" t="n">
-        <v>-225688000</v>
+        <v>-99444000</v>
       </c>
       <c r="L4" t="n">
-        <v>-19277000</v>
+        <v>-11291000</v>
       </c>
       <c r="M4" t="n">
-        <v>13322000</v>
+        <v>18634000</v>
       </c>
       <c r="N4" t="n">
-        <v>1005000</v>
+        <v>8160000</v>
       </c>
       <c r="O4" t="n">
-        <v>-236369856</v>
+        <v>-112065892.65</v>
       </c>
       <c r="P4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6743531000</v>
+        <v>5565161000</v>
       </c>
       <c r="R4" t="n">
-        <v>213828000</v>
+        <v>214906000</v>
       </c>
       <c r="S4" t="n">
-        <v>213828000</v>
+        <v>214906000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.15</v>
+        <v>-0.54</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.15</v>
+        <v>-0.54</v>
       </c>
       <c r="V4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="W4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-246372000</v>
+        <v>-116466000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7362000</v>
+        <v>-1612000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-239010000</v>
+        <v>-118078000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-10320000</v>
+        <v>-3790000</v>
       </c>
       <c r="AE4" t="n">
-        <v>10320000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3450000</v>
-      </c>
+        <v>3790000</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-19277000</v>
+        <v>-11291000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6960000</v>
+        <v>817000</v>
       </c>
       <c r="AI4" t="n">
-        <v>13322000</v>
+        <v>18634000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1005000</v>
+        <v>8160000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-209412000</v>
+        <v>-102326000</v>
       </c>
       <c r="AL4" t="n">
-        <v>697624000</v>
+        <v>630214000</v>
       </c>
       <c r="AM4" t="n">
-        <v>168493000</v>
+        <v>146902000</v>
       </c>
       <c r="AN4" t="n">
-        <v>36748000</v>
+        <v>42929000</v>
       </c>
       <c r="AO4" t="n">
-        <v>36748000</v>
+        <v>42929000</v>
       </c>
       <c r="AP4" t="n">
-        <v>205084000</v>
+        <v>147593000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>193156000</v>
+        <v>137067000</v>
       </c>
       <c r="AR4" t="n">
-        <v>11928000</v>
+        <v>10526000</v>
       </c>
       <c r="AS4" t="n">
-        <v>488212000</v>
+        <v>527888000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6045907000</v>
+        <v>4934947000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6534119000</v>
+        <v>5462835000</v>
       </c>
       <c r="AV4" t="n">
-        <v>6534119000</v>
+        <v>5462835000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2697600</v>
+        <v>-2347681.825422</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.167968</v>
       </c>
       <c r="D5" t="n">
-        <v>-321142000</v>
+        <v>108514000</v>
       </c>
       <c r="E5" t="n">
-        <v>-8992000</v>
+        <v>-13977000</v>
       </c>
       <c r="F5" t="n">
-        <v>-8992000</v>
+        <v>-13977000</v>
       </c>
       <c r="G5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="H5" t="n">
-        <v>27073000</v>
+        <v>44925000</v>
       </c>
       <c r="I5" t="n">
-        <v>4344097000</v>
+        <v>5547187000</v>
       </c>
       <c r="J5" t="n">
-        <v>-330134000</v>
+        <v>94537000</v>
       </c>
       <c r="K5" t="n">
-        <v>-357207000</v>
+        <v>49612000</v>
       </c>
       <c r="L5" t="n">
-        <v>-220467000</v>
+        <v>-15873000</v>
       </c>
       <c r="M5" t="n">
-        <v>14746000</v>
+        <v>24500000</v>
       </c>
       <c r="N5" t="n">
-        <v>3952000</v>
+        <v>8984000</v>
       </c>
       <c r="O5" t="n">
-        <v>-367759600</v>
+        <v>32523318.174578</v>
       </c>
       <c r="P5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4917465000</v>
+        <v>6216950000</v>
       </c>
       <c r="R5" t="n">
-        <v>206255000</v>
+        <v>216190000</v>
       </c>
       <c r="S5" t="n">
-        <v>206255000</v>
+        <v>216190000</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.81</v>
+        <v>0.09</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.81</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="W5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2101000</v>
+        <v>4218000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-371953000</v>
+        <v>25112000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-8992000</v>
+        <v>-12912000</v>
       </c>
       <c r="AE5" t="n">
-        <v>7637000</v>
+        <v>1548000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1355000</v>
+        <v>11364000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-220467000</v>
+        <v>-15873000</v>
       </c>
       <c r="AH5" t="n">
-        <v>209673000</v>
+        <v>357000</v>
       </c>
       <c r="AI5" t="n">
-        <v>14746000</v>
+        <v>24500000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3952000</v>
+        <v>8984000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-142492000</v>
+        <v>54961000</v>
       </c>
       <c r="AL5" t="n">
-        <v>573368000</v>
+        <v>669763000</v>
       </c>
       <c r="AM5" t="n">
-        <v>110322000</v>
+        <v>146608000</v>
       </c>
       <c r="AN5" t="n">
-        <v>27073000</v>
+        <v>44925000</v>
       </c>
       <c r="AO5" t="n">
-        <v>27073000</v>
+        <v>44925000</v>
       </c>
       <c r="AP5" t="n">
-        <v>221303000</v>
+        <v>154327000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>203275000</v>
+        <v>140981000</v>
       </c>
       <c r="AR5" t="n">
-        <v>18028000</v>
+        <v>13346000</v>
       </c>
       <c r="AS5" t="n">
-        <v>430876000</v>
+        <v>724724000</v>
       </c>
       <c r="AT5" t="n">
-        <v>4344097000</v>
+        <v>5547187000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4774973000</v>
+        <v>6271911000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4774973000</v>
+        <v>6271911000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-4294382.04</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.17862</v>
+      </c>
+      <c r="D6" t="n">
+        <v>204339000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-24042000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-24042000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55428000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7181976000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>180297000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>124869000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-22634000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29969000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7354000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>97696617.95999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8031041000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>218837000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>218837000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16951000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>94900000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-23577000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-2135000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25712000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-22634000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>29969000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>7354000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>141575000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>849065000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>176426000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55428000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55428000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>210127000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>195907000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14220000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>990640000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7181976000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8172616000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8172616000</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,806 +1659,886 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>697668</v>
-      </c>
-      <c r="C2" t="n">
-        <v>217146167</v>
-      </c>
-      <c r="D2" t="n">
-        <v>217843835</v>
-      </c>
-      <c r="E2" t="n">
-        <v>710248000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1172722000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>593247000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1694915000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1080141000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>593247000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>90682000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>612875000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1480126000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>612875000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>612875000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-698000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1404336000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1735473000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>217146000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>217146000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1595612000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>930257000</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
+        <v>1616000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>3025000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>925400000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>58149000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>867251000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>665355000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>20462000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>247322000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>32533000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>214789000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28718000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>21712000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>256283000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>831000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>5055000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>250397000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2208487000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>462991000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>6384000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>736000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>19628000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>19628000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>143801000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-142673000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>286474000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>276325000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10149000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1745496000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>18532000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>241586000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>2414000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>696731000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>696731000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>288580000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>50476000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>75385000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>371792000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="n">
-        <v>371792000</v>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>614432000</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>803037</v>
+        <v>892467</v>
       </c>
       <c r="C3" t="n">
-        <v>215413251</v>
+        <v>214803371</v>
       </c>
       <c r="D3" t="n">
-        <v>216216288</v>
+        <v>215695838</v>
       </c>
       <c r="E3" t="n">
-        <v>649641000</v>
+        <v>229095000</v>
       </c>
       <c r="F3" t="n">
-        <v>811266000</v>
+        <v>702440000</v>
       </c>
       <c r="G3" t="n">
-        <v>560660000</v>
+        <v>670106000</v>
       </c>
       <c r="H3" t="n">
-        <v>1318720000</v>
+        <v>1310865000</v>
       </c>
       <c r="I3" t="n">
-        <v>985550000</v>
+        <v>1054203000</v>
       </c>
       <c r="J3" t="n">
-        <v>560660000</v>
+        <v>670106000</v>
       </c>
       <c r="K3" t="n">
-        <v>69844000</v>
+        <v>74042000</v>
       </c>
       <c r="L3" t="n">
-        <v>577298000</v>
+        <v>682467000</v>
       </c>
       <c r="M3" t="n">
-        <v>1318720000</v>
+        <v>1299865000</v>
       </c>
       <c r="N3" t="n">
-        <v>577446000</v>
+        <v>684884000</v>
       </c>
       <c r="O3" t="n">
-        <v>148000</v>
+        <v>2417000</v>
       </c>
       <c r="P3" t="n">
-        <v>577298000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-803000</v>
-      </c>
+        <v>682467000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-1425230000</v>
+        <v>-1308764000</v>
       </c>
       <c r="S3" t="n">
-        <v>1718879000</v>
+        <v>1711745000</v>
       </c>
       <c r="T3" t="n">
-        <v>215413000</v>
+        <v>215696000</v>
       </c>
       <c r="U3" t="n">
-        <v>215413000</v>
+        <v>215696000</v>
       </c>
       <c r="V3" t="n">
-        <v>1127241000</v>
+        <v>1004016000</v>
       </c>
       <c r="W3" t="n">
-        <v>789151000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
+        <v>669577000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>2056000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>1616000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>142000</v>
+        <v>853000</v>
       </c>
       <c r="AB3" t="n">
-        <v>784910000</v>
+        <v>666631000</v>
       </c>
       <c r="AC3" t="n">
-        <v>43488000</v>
+        <v>49233000</v>
       </c>
       <c r="AD3" t="n">
-        <v>741422000</v>
+        <v>617398000</v>
       </c>
       <c r="AE3" t="n">
         <v>454000</v>
       </c>
       <c r="AF3" t="n">
-        <v>338090000</v>
+        <v>334439000</v>
       </c>
       <c r="AG3" t="n">
-        <v>8074000</v>
+        <v>2113000</v>
       </c>
       <c r="AH3" t="n">
-        <v>26356000</v>
+        <v>35809000</v>
       </c>
       <c r="AI3" t="n">
-        <v>26356000</v>
+        <v>24809000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>11000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>21090000</v>
+        <v>21156000</v>
       </c>
       <c r="AL3" t="n">
-        <v>20869000</v>
+        <v>16049000</v>
       </c>
       <c r="AM3" t="n">
-        <v>163456000</v>
+        <v>149204000</v>
       </c>
       <c r="AN3" t="n">
-        <v>681000</v>
+        <v>295000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2683000</v>
+        <v>5624000</v>
       </c>
       <c r="AP3" t="n">
-        <v>160092000</v>
+        <v>143285000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1704687000</v>
+        <v>1688900000</v>
       </c>
       <c r="AR3" t="n">
-        <v>381047000</v>
+        <v>300258000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>6119000</v>
+        <v>5772000</v>
       </c>
       <c r="AU3" t="n">
-        <v>932000</v>
+        <v>515000</v>
       </c>
       <c r="AV3" t="n">
-        <v>4716000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>6417000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>16638000</v>
+        <v>12361000</v>
       </c>
       <c r="BA3" t="n">
-        <v>16638000</v>
+        <v>12361000</v>
       </c>
       <c r="BB3" t="n">
-        <v>118999000</v>
+        <v>123490000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-119526000</v>
+        <v>-90421000</v>
       </c>
       <c r="BD3" t="n">
-        <v>238525000</v>
+        <v>213911000</v>
       </c>
       <c r="BE3" t="n">
-        <v>230779000</v>
+        <v>208014000</v>
       </c>
       <c r="BF3" t="n">
-        <v>7746000</v>
+        <v>5897000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1323640000</v>
+        <v>1388642000</v>
       </c>
       <c r="BH3" t="n">
-        <v>17921000</v>
+        <v>105028000</v>
       </c>
       <c r="BI3" t="n">
-        <v>456391000</v>
+        <v>143128000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3466000</v>
+        <v>3035000</v>
       </c>
       <c r="BK3" t="n">
-        <v>544380000</v>
+        <v>617573000</v>
       </c>
       <c r="BL3" t="n">
-        <v>544380000</v>
+        <v>617573000</v>
       </c>
       <c r="BM3" t="n">
-        <v>73920000</v>
+        <v>50978000</v>
       </c>
       <c r="BN3" t="n">
-        <v>64179000</v>
+        <v>3028000</v>
       </c>
       <c r="BO3" t="n">
-        <v>71602000</v>
+        <v>66569000</v>
       </c>
       <c r="BP3" t="n">
-        <v>91781000</v>
+        <v>399303000</v>
       </c>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="n">
-        <v>91781000</v>
+        <v>399303000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>892467</v>
+        <v>803037</v>
       </c>
       <c r="C4" t="n">
-        <v>214803371</v>
+        <v>215413251</v>
       </c>
       <c r="D4" t="n">
-        <v>215695838</v>
+        <v>216216288</v>
       </c>
       <c r="E4" t="n">
-        <v>229095000</v>
+        <v>649641000</v>
       </c>
       <c r="F4" t="n">
-        <v>702440000</v>
+        <v>811266000</v>
       </c>
       <c r="G4" t="n">
-        <v>670106000</v>
+        <v>560660000</v>
       </c>
       <c r="H4" t="n">
-        <v>1310865000</v>
+        <v>1318720000</v>
       </c>
       <c r="I4" t="n">
-        <v>1054203000</v>
+        <v>985550000</v>
       </c>
       <c r="J4" t="n">
-        <v>670106000</v>
+        <v>560660000</v>
       </c>
       <c r="K4" t="n">
-        <v>74042000</v>
+        <v>69844000</v>
       </c>
       <c r="L4" t="n">
-        <v>682467000</v>
+        <v>577298000</v>
       </c>
       <c r="M4" t="n">
-        <v>1299865000</v>
+        <v>1318720000</v>
       </c>
       <c r="N4" t="n">
-        <v>684884000</v>
+        <v>577446000</v>
       </c>
       <c r="O4" t="n">
-        <v>2417000</v>
+        <v>148000</v>
       </c>
       <c r="P4" t="n">
-        <v>682467000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>577298000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-803000</v>
+      </c>
       <c r="R4" t="n">
-        <v>-1308764000</v>
+        <v>-1425230000</v>
       </c>
       <c r="S4" t="n">
-        <v>1711745000</v>
+        <v>1718879000</v>
       </c>
       <c r="T4" t="n">
-        <v>215696000</v>
+        <v>215413000</v>
       </c>
       <c r="U4" t="n">
-        <v>215696000</v>
+        <v>215413000</v>
       </c>
       <c r="V4" t="n">
-        <v>1004016000</v>
+        <v>1127241000</v>
       </c>
       <c r="W4" t="n">
-        <v>669577000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>789151000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>1616000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>2056000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>853000</v>
+        <v>142000</v>
       </c>
       <c r="AB4" t="n">
-        <v>666631000</v>
+        <v>784910000</v>
       </c>
       <c r="AC4" t="n">
-        <v>49233000</v>
+        <v>43488000</v>
       </c>
       <c r="AD4" t="n">
-        <v>617398000</v>
+        <v>741422000</v>
       </c>
       <c r="AE4" t="n">
         <v>454000</v>
       </c>
       <c r="AF4" t="n">
-        <v>334439000</v>
+        <v>338090000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2113000</v>
+        <v>8074000</v>
       </c>
       <c r="AH4" t="n">
-        <v>35809000</v>
+        <v>26356000</v>
       </c>
       <c r="AI4" t="n">
-        <v>24809000</v>
+        <v>26356000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>21156000</v>
+        <v>21090000</v>
       </c>
       <c r="AL4" t="n">
-        <v>16049000</v>
+        <v>20869000</v>
       </c>
       <c r="AM4" t="n">
-        <v>149204000</v>
+        <v>163456000</v>
       </c>
       <c r="AN4" t="n">
-        <v>295000</v>
+        <v>681000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5624000</v>
+        <v>2683000</v>
       </c>
       <c r="AP4" t="n">
-        <v>143285000</v>
+        <v>160092000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1688900000</v>
+        <v>1704687000</v>
       </c>
       <c r="AR4" t="n">
-        <v>300258000</v>
+        <v>381047000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>5772000</v>
+        <v>6119000</v>
       </c>
       <c r="AU4" t="n">
-        <v>515000</v>
+        <v>932000</v>
       </c>
       <c r="AV4" t="n">
-        <v>6417000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>4716000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>12361000</v>
+        <v>16638000</v>
       </c>
       <c r="BA4" t="n">
-        <v>12361000</v>
+        <v>16638000</v>
       </c>
       <c r="BB4" t="n">
-        <v>123490000</v>
+        <v>118999000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-90421000</v>
+        <v>-119526000</v>
       </c>
       <c r="BD4" t="n">
-        <v>213911000</v>
+        <v>238525000</v>
       </c>
       <c r="BE4" t="n">
-        <v>208014000</v>
+        <v>230779000</v>
       </c>
       <c r="BF4" t="n">
-        <v>5897000</v>
+        <v>7746000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1388642000</v>
+        <v>1323640000</v>
       </c>
       <c r="BH4" t="n">
-        <v>105028000</v>
+        <v>17921000</v>
       </c>
       <c r="BI4" t="n">
-        <v>143128000</v>
+        <v>456391000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3035000</v>
+        <v>3466000</v>
       </c>
       <c r="BK4" t="n">
-        <v>617573000</v>
+        <v>544380000</v>
       </c>
       <c r="BL4" t="n">
-        <v>617573000</v>
+        <v>544380000</v>
       </c>
       <c r="BM4" t="n">
-        <v>50978000</v>
+        <v>73920000</v>
       </c>
       <c r="BN4" t="n">
-        <v>3028000</v>
+        <v>64179000</v>
       </c>
       <c r="BO4" t="n">
-        <v>66569000</v>
+        <v>71602000</v>
       </c>
       <c r="BP4" t="n">
-        <v>399303000</v>
+        <v>91781000</v>
       </c>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
-        <v>399303000</v>
+        <v>91781000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>802854</v>
+        <v>697668</v>
       </c>
       <c r="C5" t="n">
-        <v>212335146</v>
+        <v>217146167</v>
       </c>
       <c r="D5" t="n">
-        <v>213138000</v>
+        <v>217843835</v>
       </c>
       <c r="E5" t="n">
-        <v>279331000</v>
+        <v>710248000</v>
       </c>
       <c r="F5" t="n">
-        <v>387640000</v>
+        <v>1172722000</v>
       </c>
       <c r="G5" t="n">
-        <v>920896000</v>
+        <v>593247000</v>
       </c>
       <c r="H5" t="n">
-        <v>1251014000</v>
+        <v>1694915000</v>
       </c>
       <c r="I5" t="n">
-        <v>1152162000</v>
+        <v>1080141000</v>
       </c>
       <c r="J5" t="n">
-        <v>920896000</v>
+        <v>593247000</v>
       </c>
       <c r="K5" t="n">
-        <v>57640000</v>
+        <v>90682000</v>
       </c>
       <c r="L5" t="n">
-        <v>921014000</v>
+        <v>612875000</v>
       </c>
       <c r="M5" t="n">
-        <v>1251014000</v>
+        <v>1480126000</v>
       </c>
       <c r="N5" t="n">
-        <v>921014000</v>
+        <v>612875000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>921014000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>612875000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-698000</v>
+      </c>
       <c r="R5" t="n">
-        <v>-1062391000</v>
+        <v>-1404336000</v>
       </c>
       <c r="S5" t="n">
-        <v>1679904000</v>
+        <v>1735473000</v>
       </c>
       <c r="T5" t="n">
-        <v>213138000</v>
+        <v>217146000</v>
       </c>
       <c r="U5" t="n">
-        <v>213138000</v>
+        <v>217146000</v>
       </c>
       <c r="V5" t="n">
-        <v>705895000</v>
+        <v>1595612000</v>
       </c>
       <c r="W5" t="n">
-        <v>369945000</v>
+        <v>930257000</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>1616000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3025000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>368117000</v>
+        <v>925400000</v>
       </c>
       <c r="AC5" t="n">
-        <v>38117000</v>
+        <v>58149000</v>
       </c>
       <c r="AD5" t="n">
-        <v>330000000</v>
+        <v>867251000</v>
       </c>
       <c r="AE5" t="n">
         <v>95000</v>
       </c>
       <c r="AF5" t="n">
-        <v>335950000</v>
+        <v>665355000</v>
       </c>
       <c r="AG5" t="n">
-        <v>6089000</v>
+        <v>20462000</v>
       </c>
       <c r="AH5" t="n">
-        <v>19523000</v>
+        <v>247322000</v>
       </c>
       <c r="AI5" t="n">
-        <v>19523000</v>
+        <v>32533000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>214789000</v>
       </c>
       <c r="AK5" t="n">
-        <v>20297000</v>
+        <v>28718000</v>
       </c>
       <c r="AL5" t="n">
-        <v>18616000</v>
+        <v>21712000</v>
       </c>
       <c r="AM5" t="n">
-        <v>172611000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>256283000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>831000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>1581000</v>
+        <v>5055000</v>
       </c>
       <c r="AP5" t="n">
-        <v>171030000</v>
+        <v>250397000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1626909000</v>
+        <v>2208487000</v>
       </c>
       <c r="AR5" t="n">
-        <v>138797000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7000</v>
-      </c>
+        <v>462991000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>12102000</v>
+        <v>6384000</v>
       </c>
       <c r="AU5" t="n">
-        <v>948000</v>
+        <v>736000</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
-      <c r="AW5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>19628000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>19628000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>143801000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-142673000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>286474000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>276325000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10149000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1745496000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>18532000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>241586000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2414000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>696731000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>696731000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>288580000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>50476000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>75385000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>371792000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="n">
+        <v>371792000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>467035</v>
+      </c>
+      <c r="C6" t="n">
+        <v>220367681</v>
+      </c>
+      <c r="D6" t="n">
+        <v>220834716</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1356162000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1696911000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>686524000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2309399000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1459727000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>686524000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>95047000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>707535000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2030830000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>707535000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>707535000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-1326387000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1755713000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220835000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>220835000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2162409000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1386779000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>4686000</v>
+      </c>
+      <c r="AA6" t="n">
         <v>0</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>118000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>118000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>84092000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-69069000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>153161000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>151851000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1310000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1488112000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>91492000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>55984000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1816000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>583549000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>583549000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>26900000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>868000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>62402000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>665101000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>614432000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>50669000</v>
+      <c r="AB6" t="n">
+        <v>1381535000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>58240000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1323295000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>95000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>775630000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>18554000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>315376000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>36807000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>278569000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34433000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>25821000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>272970000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>978000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>16204000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>255788000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2869944000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>634587000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>7004000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>417000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>368000</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>21011000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>21011000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>156508000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-167601000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>324109000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>311452000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>12657000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2235357000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>17816000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>358268000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2023000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1057654000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1057654000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>405258000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>58190000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>90446000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>245702000</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>245702000</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2620,483 +2756,564 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Other Cash Adjustment Outside Changein Cash</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-239975000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1007603000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1347944000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-20250000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>613378000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>548172000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>65206000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>302727000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>340341000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>340341000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-1007603000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1347944000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-17796000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-4370000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-4370000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-13426000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2454000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-15880000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-219725000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-2141000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8984000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-24974000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-330585000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>104671000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-435256000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>39880000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17843000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>484000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4218000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>44925000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1008060000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>1008060000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1008060000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-615155000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>821530000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1436685000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>44925000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>747000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>20894000</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-78659000</v>
+        <v>-439406000</v>
       </c>
       <c r="C3" t="n">
-        <v>-945000000</v>
+        <v>-614640000</v>
       </c>
       <c r="D3" t="n">
-        <v>1058605000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>915523000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-23230000</v>
+        <v>-47042000</v>
       </c>
       <c r="G3" t="n">
-        <v>548172000</v>
+        <v>542431000</v>
       </c>
       <c r="H3" t="n">
-        <v>542431000</v>
+        <v>106653000</v>
       </c>
       <c r="I3" t="n">
-        <v>5741000</v>
+        <v>435778000</v>
       </c>
       <c r="J3" t="n">
-        <v>80384000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>270694000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
-        <v>113605000</v>
+        <v>300883000</v>
       </c>
       <c r="N3" t="n">
-        <v>113605000</v>
+        <v>300883000</v>
       </c>
       <c r="O3" t="n">
-        <v>-945000000</v>
+        <v>-614640000</v>
       </c>
       <c r="P3" t="n">
-        <v>1058605000</v>
+        <v>915523000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-19214000</v>
+        <v>557448000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>603537000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>607010000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-3473000</v>
       </c>
       <c r="U3" t="n">
-        <v>-5178000</v>
+        <v>-12801000</v>
       </c>
       <c r="V3" t="n">
-        <v>-5178000</v>
+        <v>-12801000</v>
       </c>
       <c r="W3" t="n">
-        <v>-14036000</v>
+        <v>-33288000</v>
       </c>
       <c r="X3" t="n">
-        <v>4016000</v>
+        <v>953000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-18052000</v>
+        <v>-34241000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-55429000</v>
+        <v>-392364000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4093000</v>
+        <v>-5049000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7870000</v>
+        <v>688000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-17786000</v>
+        <v>-12257000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-7354000</v>
+        <v>-220428000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2711000</v>
+        <v>-20996000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-10065000</v>
+        <v>-197224000</v>
       </c>
       <c r="AG3" t="n">
-        <v>19912000</v>
+        <v>36453000</v>
       </c>
       <c r="AH3" t="n">
-        <v>13067000</v>
+        <v>8029000</v>
       </c>
       <c r="AI3" t="n">
-        <v>4820000</v>
+        <v>-2208000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1612000</v>
+        <v>7362000</v>
       </c>
       <c r="AK3" t="n">
-        <v>42929000</v>
+        <v>36748000</v>
       </c>
       <c r="AL3" t="n">
-        <v>899000</v>
+        <v>558000</v>
       </c>
       <c r="AM3" t="n">
-        <v>42929000</v>
+        <v>36190000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3284000</v>
+        <v>2462000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-116466000</v>
-      </c>
+        <v>-246372000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-439406000</v>
+        <v>-78659000</v>
       </c>
       <c r="C4" t="n">
-        <v>-614640000</v>
+        <v>-945000000</v>
       </c>
       <c r="D4" t="n">
-        <v>915523000</v>
-      </c>
-      <c r="E4" t="n">
+        <v>1058605000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>-23230000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>548172000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>542431000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5741000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>80384000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>113605000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>113605000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-945000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1058605000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-19214000</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>-47042000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>542431000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>106653000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>435778000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>270694000</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>300883000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>300883000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-614640000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>915523000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>557448000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>603537000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>607010000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-3473000</v>
-      </c>
       <c r="U4" t="n">
-        <v>-12801000</v>
+        <v>-5178000</v>
       </c>
       <c r="V4" t="n">
-        <v>-12801000</v>
+        <v>-5178000</v>
       </c>
       <c r="W4" t="n">
-        <v>-33288000</v>
+        <v>-14036000</v>
       </c>
       <c r="X4" t="n">
-        <v>953000</v>
+        <v>4016000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-34241000</v>
+        <v>-18052000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-392364000</v>
+        <v>-55429000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-5049000</v>
+        <v>-4093000</v>
       </c>
       <c r="AB4" t="n">
-        <v>688000</v>
+        <v>7870000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-12257000</v>
+        <v>-17786000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-220428000</v>
+        <v>-7354000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-20996000</v>
+        <v>2711000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-197224000</v>
+        <v>-10065000</v>
       </c>
       <c r="AG4" t="n">
-        <v>36453000</v>
+        <v>19912000</v>
       </c>
       <c r="AH4" t="n">
-        <v>8029000</v>
+        <v>13067000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2208000</v>
+        <v>4820000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7362000</v>
+        <v>-1612000</v>
       </c>
       <c r="AK4" t="n">
-        <v>36748000</v>
+        <v>42929000</v>
       </c>
       <c r="AL4" t="n">
-        <v>558000</v>
+        <v>899000</v>
       </c>
       <c r="AM4" t="n">
-        <v>36190000</v>
+        <v>42929000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2462000</v>
+        <v>3284000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-246372000</v>
-      </c>
+        <v>-116466000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-493908000</v>
+        <v>-239975000</v>
       </c>
       <c r="C5" t="n">
-        <v>-247349000</v>
+        <v>-1007603000</v>
       </c>
       <c r="D5" t="n">
-        <v>345000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1008060000</v>
-      </c>
+        <v>1347944000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-26659000</v>
+        <v>-20250000</v>
       </c>
       <c r="G5" t="n">
-        <v>106653000</v>
+        <v>613378000</v>
       </c>
       <c r="H5" t="n">
-        <v>157251000</v>
+        <v>548172000</v>
       </c>
       <c r="I5" t="n">
-        <v>-50598000</v>
+        <v>65206000</v>
       </c>
       <c r="J5" t="n">
-        <v>1056460000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1008060000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1008060000</v>
-      </c>
+        <v>302727000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>97651000</v>
+        <v>340341000</v>
       </c>
       <c r="N5" t="n">
-        <v>97651000</v>
+        <v>340341000</v>
       </c>
       <c r="O5" t="n">
-        <v>-247349000</v>
+        <v>-1007603000</v>
       </c>
       <c r="P5" t="n">
-        <v>345000000</v>
+        <v>1347944000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-639809000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-615155000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>821530000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1436685000</v>
-      </c>
+        <v>-17796000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-40000</v>
+        <v>-4370000</v>
       </c>
       <c r="V5" t="n">
-        <v>-40000</v>
+        <v>-4370000</v>
       </c>
       <c r="W5" t="n">
-        <v>-24614000</v>
+        <v>-13426000</v>
       </c>
       <c r="X5" t="n">
-        <v>2005000</v>
+        <v>2454000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-26619000</v>
+        <v>-15880000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-467249000</v>
+        <v>-219725000</v>
       </c>
       <c r="AA5" t="n">
-        <v>321000</v>
+        <v>-2141000</v>
       </c>
       <c r="AB5" t="n">
-        <v>4121000</v>
+        <v>8984000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9142000</v>
+        <v>-24974000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-361629000</v>
+        <v>-330585000</v>
       </c>
       <c r="AE5" t="n">
-        <v>154457000</v>
+        <v>104671000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-516086000</v>
+        <v>-435256000</v>
       </c>
       <c r="AG5" t="n">
-        <v>226779000</v>
+        <v>39880000</v>
       </c>
       <c r="AH5" t="n">
-        <v>5688000</v>
+        <v>17843000</v>
       </c>
       <c r="AI5" t="n">
-        <v>11493000</v>
+        <v>484000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2101000</v>
+        <v>4218000</v>
       </c>
       <c r="AK5" t="n">
-        <v>27073000</v>
+        <v>44925000</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>27073000</v>
+        <v>44925000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>747000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-374054000</v>
+        <v>20894000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-488653000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-757624000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1278469000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-25584000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>603970000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>613378000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-9407000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>476924000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>520845000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>520845000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-757624000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1278469000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-23262000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>-3296000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-3296000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-19965000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2323000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-22288000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-463069000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-4262000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7354000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-29970000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-664782000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>40217000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-704999000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>58132000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>15822000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4109000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16951000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>55428000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>55428000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>201000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>77949000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1000</v>
       </c>
     </row>
   </sheetData>
@@ -3641,182 +3858,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3841,10 +4058,8 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>10961</t>
-        </is>
+      <c r="C2" t="n">
+        <v>10961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3925,7 +4140,7 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1672444800</v>
@@ -3942,64 +4157,64 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.52</v>
+        <v>25.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>23.6</v>
+        <v>21.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.5</v>
+        <v>21.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.6</v>
+        <v>22.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>22.52</v>
+        <v>25.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>23.6</v>
+        <v>21.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>22.5</v>
+        <v>21.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.6</v>
+        <v>22.84</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.788</v>
+        <v>1.846</v>
       </c>
       <c r="AK2" t="n">
-        <v>63.5</v>
+        <v>74.90909000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="AN2" t="n">
         <v>103</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22.32</v>
+        <v>23.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>23.4</v>
+        <v>25.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>5032790016</v>
+        <v>5442281984</v>
       </c>
       <c r="AT2" t="n">
-        <v>4940323865</v>
+        <v>5693260925</v>
       </c>
       <c r="AU2" t="n">
         <v>16.14</v>
@@ -4014,13 +4229,13 @@
         <v>16.14</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.5806969400000001</v>
+        <v>0.6279452</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.9882</v>
+        <v>20.5398</v>
       </c>
       <c r="BA2" t="n">
-        <v>23.63495</v>
+        <v>23.21215</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
@@ -4037,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>6166701568</v>
+        <v>6334536192</v>
       </c>
       <c r="BG2" t="n">
         <v>0.008569999999999999</v>
@@ -4049,10 +4264,10 @@
         <v>220157035</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.30905</v>
+        <v>0.30876</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71989995</v>
+        <v>0.73850995</v>
       </c>
       <c r="BL2" t="n">
         <v>220157035</v>
@@ -4061,7 +4276,7 @@
         <v>3.204</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.1348314</v>
+        <v>7.7153554</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4079,19 +4294,19 @@
         <v>74239000</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.712</v>
+        <v>0.731</v>
       </c>
       <c r="BV2" t="n">
-        <v>46.423</v>
+        <v>47.687</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.12220448</v>
+        <v>-0.035621226</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4099,7 +4314,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>22.86</v>
+        <v>24.72</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4198,137 +4413,137 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>0.34000015</v>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>AUTO1 Group SE</t>
+        </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>22.5 - 23.6</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>1781010154</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>finmb_337644871</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-4.776579</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1747983600000</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-1.2399998</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>21.78 - 22.84</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DE2" t="n">
+      <c r="DT2" t="n">
         <v>103</v>
       </c>
-      <c r="DF2" t="n">
-        <v>6.720001</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.41635698</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DU2" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.5315985</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>16.14 - 31.94</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>-9.08</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.284283</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-12.2204485</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DX2" t="n">
+        <v>-7.220001</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.22604887</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-3.5621226</v>
+      </c>
+      <c r="EA2" t="n">
         <v>1774971000</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="EB2" t="n">
         <v>1775057400</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="EC2" t="n">
         <v>1775057400</v>
       </c>
-      <c r="DO2" t="b">
+      <c r="ED2" t="b">
         <v>1</v>
       </c>
-      <c r="DP2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>3.8718014</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.20390566</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.77495</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.032788306</v>
-      </c>
-      <c r="DU2" t="n">
+      <c r="EE2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>4.1801987</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.203517</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1.5078487</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.06495946</v>
+      </c>
+      <c r="EJ2" t="n">
         <v>20</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EK2" t="n">
         <v>15</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1779695622</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_337644871</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1747983600000</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>AUTO1 Group SE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.5097697</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>22.86</v>
-      </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr"/>
